--- a/DOCP_optimization_3bus_example_RF=0_and_RF=10.xlsx
+++ b/DOCP_optimization_3bus_example_RF=0_and_RF=10.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pm.deoliveiradejes/Dropbox (Personal)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\GitHub\Optimal_DOCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEC3124-AEA2-4944-948A-D90A78FBA9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FF0ACA-A782-401C-A83C-418FE24D711D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="500" windowWidth="37920" windowHeight="21100" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A2977F88-2306-084C-88E0-6AF9B986A493}"/>
   </bookViews>
   <sheets>
     <sheet name="RF=0 and 10" sheetId="7" r:id="rId1"/>
     <sheet name="RF=0" sheetId="3" r:id="rId2"/>
     <sheet name="RF=10" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="alpha1" localSheetId="0">'RF=0 and 10'!$AC$2</definedName>
@@ -68,7 +67,7 @@
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'RF=0 and 10'!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'RF=10'!$Q$21:$Q$26</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">'RF=0'!$S$21:$S$32</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'RF=0 and 10'!$S$21:$S$32</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'RF=0 and 10'!$S$21:$S$44</definedName>
     <definedName name="solver_lhs3" localSheetId="2" hidden="1">'RF=10'!$S$21:$S$32</definedName>
     <definedName name="solver_lin" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">1</definedName>
@@ -115,15 +114,15 @@
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">1.1</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1.1</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">1.1</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">0.1</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.1</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">0.1</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">0.2</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">0.2</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">0.2</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'RF=0'!$U$28</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'RF=0 and 10'!$U$28</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'RF=10'!$U$28</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'RF=0'!$U$29</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'RF=0 and 10'!$U$29</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'RF=10'!$U$29</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'RF=0'!$U$30</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'RF=0 and 10'!$U$30</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">'RF=10'!$U$30</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -151,9 +150,9 @@
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_ver" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -197,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="54">
   <si>
     <t>B</t>
   </si>
@@ -487,6 +486,15 @@
   <si>
     <t>Rf=10</t>
   </si>
+  <si>
+    <t>Dmax</t>
+  </si>
+  <si>
+    <t>Dmin</t>
+  </si>
+  <si>
+    <t>CTI</t>
+  </si>
 </sst>
 </file>
 
@@ -497,7 +505,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -839,21 +847,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -867,6 +860,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -912,8 +920,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8173357" y="7237488"/>
-          <a:ext cx="4732735" cy="1966467"/>
+          <a:off x="8228920" y="7144884"/>
+          <a:ext cx="4730089" cy="1940009"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -9674,8 +9682,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7548940" y="7237488"/>
-          <a:ext cx="4732736" cy="1966467"/>
+          <a:off x="7554232" y="7052279"/>
+          <a:ext cx="4716860" cy="1913551"/>
           <a:chOff x="1999434" y="4061335"/>
           <a:chExt cx="4713081" cy="1951348"/>
         </a:xfrm>
@@ -18365,9 +18373,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -18405,7 +18413,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -18511,7 +18519,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -18653,7 +18661,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -18665,7 +18673,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B1:AC44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="1.1640625" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" customWidth="1"/>
@@ -18683,13 +18691,13 @@
     <col min="28" max="28" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB1" s="57" t="s">
+    <row r="1" spans="2:29">
+      <c r="AB1" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="57"/>
+      <c r="AC1" s="63"/>
     </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:29">
       <c r="AB2" s="45" t="s">
         <v>30</v>
       </c>
@@ -18697,15 +18705,15 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="S3" s="55" t="s">
+    <row r="3" spans="2:29">
+      <c r="S3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55" t="s">
+      <c r="T3" s="65"/>
+      <c r="U3" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="65"/>
       <c r="AB3" s="45" t="s">
         <v>31</v>
       </c>
@@ -18713,7 +18721,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:29">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -18725,38 +18733,38 @@
         <v>24</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58" t="s">
+      <c r="H4" s="61"/>
+      <c r="I4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58" t="s">
+      <c r="J4" s="61"/>
+      <c r="K4" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58" t="s">
+      <c r="L4" s="61"/>
+      <c r="M4" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="58"/>
-      <c r="O4" s="54" t="s">
+      <c r="N4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54" t="s">
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54" t="s">
+      <c r="R4" s="62"/>
+      <c r="S4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="62"/>
+      <c r="U4" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="54"/>
+      <c r="V4" s="62"/>
       <c r="W4" s="3"/>
       <c r="X4" s="2" t="s">
         <v>25</v>
@@ -18764,7 +18772,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:29">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -18844,7 +18852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:29">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -18930,7 +18938,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:29">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -19016,7 +19024,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:29">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -19102,7 +19110,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:29">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -19188,7 +19196,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:29">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -19274,7 +19282,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:29">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -19360,7 +19368,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:29">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -19440,7 +19448,7 @@
         <v>2.7733147409998602</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:29">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -19520,7 +19528,7 @@
         <v>1.98644662417039</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:29">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -19600,7 +19608,7 @@
         <v>-0.171158780969107</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:29">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -19680,7 +19688,7 @@
         <v>5.3875475690367098</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:29">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -19760,7 +19768,7 @@
         <v>2.4162494488161599</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -19840,31 +19848,31 @@
         <v>2.7314117620923599</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:27">
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="T19" s="55" t="s">
+    <row r="19" spans="2:27">
+      <c r="T19" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="U19" s="55"/>
+      <c r="U19" s="65"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27">
       <c r="I20" s="1" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K20" s="56" t="s">
+      <c r="K20" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
       <c r="Q20" s="10" t="s">
         <v>2</v>
       </c>
@@ -19873,38 +19881,38 @@
       </c>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:27">
       <c r="F21" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="63">
+      <c r="H21" s="58">
         <v>1</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I21" s="59">
         <v>1</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J21" s="59">
         <v>1</v>
       </c>
-      <c r="K21" s="65">
+      <c r="K21" s="60">
         <v>-2.4198556495023702</v>
       </c>
-      <c r="L21" s="65">
+      <c r="L21" s="60">
         <v>0</v>
       </c>
-      <c r="M21" s="65">
+      <c r="M21" s="60">
         <v>0</v>
       </c>
-      <c r="N21" s="65">
+      <c r="N21" s="60">
         <v>0</v>
       </c>
-      <c r="O21" s="65">
+      <c r="O21" s="60">
         <v>2.93926369586231</v>
       </c>
-      <c r="P21" s="65">
+      <c r="P21" s="60">
         <v>0</v>
       </c>
-      <c r="Q21" s="59">
+      <c r="Q21" s="54">
         <v>0.11292606172105862</v>
       </c>
       <c r="S21" s="19" cm="1">
@@ -19921,35 +19929,35 @@
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H22" s="63">
+    <row r="22" spans="2:27">
+      <c r="H22" s="58">
         <v>2</v>
       </c>
-      <c r="I22" s="64">
+      <c r="I22" s="59">
         <v>1</v>
       </c>
-      <c r="J22" s="64">
+      <c r="J22" s="59">
         <v>1</v>
       </c>
-      <c r="K22" s="65">
+      <c r="K22" s="60">
         <v>5.5708124195275497</v>
       </c>
-      <c r="L22" s="65">
+      <c r="L22" s="60">
         <v>0</v>
       </c>
-      <c r="M22" s="65">
+      <c r="M22" s="60">
         <v>-2.5921016309279299</v>
       </c>
-      <c r="N22" s="65">
+      <c r="N22" s="60">
         <v>0</v>
       </c>
-      <c r="O22" s="65">
+      <c r="O22" s="60">
         <v>0</v>
       </c>
-      <c r="P22" s="65">
+      <c r="P22" s="60">
         <v>0</v>
       </c>
-      <c r="Q22" s="59">
+      <c r="Q22" s="54">
         <v>0.21208992313445765</v>
       </c>
       <c r="S22" s="19">
@@ -19965,35 +19973,35 @@
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H23" s="63">
+    <row r="23" spans="2:27">
+      <c r="H23" s="58">
         <v>3</v>
       </c>
-      <c r="I23" s="64">
+      <c r="I23" s="59">
         <v>1</v>
       </c>
-      <c r="J23" s="64">
+      <c r="J23" s="59">
         <v>1</v>
       </c>
-      <c r="K23" s="65">
+      <c r="K23" s="60">
         <v>0</v>
       </c>
-      <c r="L23" s="65">
+      <c r="L23" s="60">
         <v>0</v>
       </c>
-      <c r="M23" s="65">
+      <c r="M23" s="60">
         <v>2.8243458766258902</v>
       </c>
-      <c r="N23" s="65">
+      <c r="N23" s="60">
         <v>0</v>
       </c>
-      <c r="O23" s="65">
+      <c r="O23" s="60">
         <v>-1.6615561712812701</v>
       </c>
-      <c r="P23" s="65">
+      <c r="P23" s="60">
         <v>0</v>
       </c>
-      <c r="Q23" s="59">
+      <c r="Q23" s="54">
         <v>0.16553745501498754</v>
       </c>
       <c r="R23" s="10" t="s">
@@ -20012,35 +20020,35 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H24" s="63">
+    <row r="24" spans="2:27">
+      <c r="H24" s="58">
         <v>4</v>
       </c>
-      <c r="I24" s="64">
+      <c r="I24" s="59">
         <v>2</v>
       </c>
-      <c r="J24" s="64">
+      <c r="J24" s="59">
         <v>2</v>
       </c>
-      <c r="K24" s="65">
+      <c r="K24" s="60">
         <v>0</v>
       </c>
-      <c r="L24" s="65">
+      <c r="L24" s="60">
         <v>0</v>
       </c>
-      <c r="M24" s="65">
+      <c r="M24" s="60">
         <v>0.55808696516542999</v>
       </c>
-      <c r="N24" s="65">
+      <c r="N24" s="60">
         <v>-2.7934300498087401</v>
       </c>
-      <c r="O24" s="65">
+      <c r="O24" s="60">
         <v>0</v>
       </c>
-      <c r="P24" s="65">
+      <c r="P24" s="60">
         <v>4.5787467516253102</v>
       </c>
-      <c r="Q24" s="59">
+      <c r="Q24" s="54">
         <v>0.18386890545629644</v>
       </c>
       <c r="S24" s="19">
@@ -20056,35 +20064,35 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H25" s="63">
+    <row r="25" spans="2:27">
+      <c r="H25" s="58">
         <v>5</v>
       </c>
-      <c r="I25" s="64">
+      <c r="I25" s="59">
         <v>3</v>
       </c>
-      <c r="J25" s="64">
+      <c r="J25" s="59">
         <v>3</v>
       </c>
-      <c r="K25" s="65">
+      <c r="K25" s="60">
         <v>2.7693621834472499</v>
       </c>
-      <c r="L25" s="65">
+      <c r="L25" s="60">
         <v>-2.24616609413899</v>
       </c>
-      <c r="M25" s="65">
+      <c r="M25" s="60">
         <v>0</v>
       </c>
-      <c r="N25" s="65">
+      <c r="N25" s="60">
         <v>6.0409597033869904</v>
       </c>
-      <c r="O25" s="65">
+      <c r="O25" s="60">
         <v>0</v>
       </c>
-      <c r="P25" s="65">
+      <c r="P25" s="60">
         <v>0</v>
       </c>
-      <c r="Q25" s="59">
+      <c r="Q25" s="54">
         <v>0.16101473613884532</v>
       </c>
       <c r="S25" s="19">
@@ -20100,35 +20108,35 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H26" s="63">
+    <row r="26" spans="2:27">
+      <c r="H26" s="58">
         <v>6</v>
       </c>
-      <c r="I26" s="64">
+      <c r="I26" s="59">
         <v>3</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="59">
         <v>4</v>
       </c>
-      <c r="K26" s="65">
+      <c r="K26" s="60">
         <v>0</v>
       </c>
-      <c r="L26" s="65">
+      <c r="L26" s="60">
         <v>4.86990509840349</v>
       </c>
-      <c r="M26" s="65">
+      <c r="M26" s="60">
         <v>0</v>
       </c>
-      <c r="N26" s="65">
+      <c r="N26" s="60">
         <v>0</v>
       </c>
-      <c r="O26" s="65">
+      <c r="O26" s="60">
         <v>1.41180264048991</v>
       </c>
-      <c r="P26" s="65">
+      <c r="P26" s="60">
         <v>-3.9783456200974499</v>
       </c>
-      <c r="Q26" s="59">
+      <c r="Q26" s="54">
         <v>0.15399694630374194</v>
       </c>
       <c r="S26" s="19">
@@ -20142,32 +20150,32 @@
         <v>0.26753502849872379</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H27" s="63">
+    <row r="27" spans="2:27">
+      <c r="H27" s="58">
         <v>7</v>
       </c>
-      <c r="I27" s="64">
+      <c r="I27" s="59">
         <v>1</v>
       </c>
-      <c r="J27" s="64">
+      <c r="J27" s="59">
         <v>1</v>
       </c>
-      <c r="K27" s="65">
+      <c r="K27" s="60">
         <v>0</v>
       </c>
-      <c r="L27" s="65">
+      <c r="L27" s="60">
         <v>-1.5719399875761499</v>
       </c>
-      <c r="M27" s="65">
+      <c r="M27" s="60">
         <v>0</v>
       </c>
-      <c r="N27" s="65">
+      <c r="N27" s="60">
         <v>2.90093982891407</v>
       </c>
-      <c r="O27" s="65">
+      <c r="O27" s="60">
         <v>0</v>
       </c>
-      <c r="P27" s="65">
+      <c r="P27" s="60">
         <v>0</v>
       </c>
       <c r="S27" s="19">
@@ -20181,131 +20189,149 @@
         <v>2.1096723618329807</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H28" s="63">
+    <row r="28" spans="2:27">
+      <c r="H28" s="58">
         <v>8</v>
       </c>
-      <c r="I28" s="64">
+      <c r="I28" s="59">
         <v>1</v>
       </c>
-      <c r="J28" s="64">
+      <c r="J28" s="59">
         <v>1</v>
       </c>
-      <c r="K28" s="65">
+      <c r="K28" s="60">
         <v>7.2922928986111604</v>
       </c>
-      <c r="L28" s="65">
+      <c r="L28" s="60">
         <v>0</v>
       </c>
-      <c r="M28" s="65">
+      <c r="M28" s="60">
         <v>-2.82434134423734</v>
       </c>
-      <c r="N28" s="65">
+      <c r="N28" s="60">
         <v>0</v>
       </c>
-      <c r="O28" s="65">
+      <c r="O28" s="60">
         <v>0</v>
       </c>
-      <c r="P28" s="65">
+      <c r="P28" s="60">
         <v>0</v>
       </c>
       <c r="Q28" s="48"/>
       <c r="S28" s="19">
         <v>0.35595563973794331</v>
       </c>
+      <c r="T28" t="s">
+        <v>51</v>
+      </c>
+      <c r="U28">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H29" s="63">
+    <row r="29" spans="2:27">
+      <c r="H29" s="58">
         <v>9</v>
       </c>
-      <c r="I29" s="64">
+      <c r="I29" s="59">
         <v>1</v>
       </c>
-      <c r="J29" s="64">
+      <c r="J29" s="59">
         <v>1</v>
       </c>
-      <c r="K29" s="65">
+      <c r="K29" s="60">
         <v>0</v>
       </c>
-      <c r="L29" s="65">
+      <c r="L29" s="60">
         <v>2.4589154712991199</v>
       </c>
-      <c r="M29" s="65">
+      <c r="M29" s="60">
         <v>0</v>
       </c>
-      <c r="N29" s="65">
+      <c r="N29" s="60">
         <v>0</v>
       </c>
-      <c r="O29" s="65">
+      <c r="O29" s="60">
         <v>0</v>
       </c>
-      <c r="P29" s="65">
+      <c r="P29" s="60">
         <v>-2.0877764203701399</v>
       </c>
       <c r="Q29" s="48"/>
       <c r="S29" s="19">
         <v>0.20000000000000007</v>
       </c>
+      <c r="T29" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29">
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H30" s="63">
+    <row r="30" spans="2:27">
+      <c r="H30" s="58">
         <v>10</v>
       </c>
-      <c r="I30" s="64">
+      <c r="I30" s="59">
         <v>2</v>
       </c>
-      <c r="J30" s="64">
+      <c r="J30" s="59">
         <v>2</v>
       </c>
-      <c r="K30" s="65">
+      <c r="K30" s="60">
         <v>0</v>
       </c>
-      <c r="L30" s="65">
+      <c r="L30" s="60">
         <v>0</v>
       </c>
-      <c r="M30" s="65">
+      <c r="M30" s="60">
         <v>0.33115615355674399</v>
       </c>
-      <c r="N30" s="65">
+      <c r="N30" s="60">
         <v>-2.5652549319377602</v>
       </c>
-      <c r="O30" s="65">
+      <c r="O30" s="60">
         <v>0</v>
       </c>
-      <c r="P30" s="65">
+      <c r="P30" s="60">
         <v>4.0056110493435</v>
       </c>
       <c r="Q30" s="48"/>
       <c r="S30" s="19">
         <v>0.20000000000000007</v>
       </c>
+      <c r="T30" t="s">
+        <v>53</v>
+      </c>
+      <c r="U30">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H31" s="63">
+    <row r="31" spans="2:27">
+      <c r="H31" s="58">
         <v>11</v>
       </c>
-      <c r="I31" s="64">
+      <c r="I31" s="59">
         <v>3</v>
       </c>
-      <c r="J31" s="64">
+      <c r="J31" s="59">
         <v>4</v>
       </c>
-      <c r="K31" s="65">
+      <c r="K31" s="60">
         <v>-4.7456997913586303</v>
       </c>
-      <c r="L31" s="65">
+      <c r="L31" s="60">
         <v>1.3391162805101799</v>
       </c>
-      <c r="M31" s="65">
+      <c r="M31" s="60">
         <v>0</v>
       </c>
-      <c r="N31" s="65">
+      <c r="N31" s="60">
         <v>0</v>
       </c>
-      <c r="O31" s="65">
+      <c r="O31" s="60">
         <v>5.9122269168042001</v>
       </c>
-      <c r="P31" s="65">
+      <c r="P31" s="60">
         <v>0</v>
       </c>
       <c r="Q31" s="48"/>
@@ -20313,32 +20339,32 @@
         <v>0.70005553845513246</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="H32" s="63">
+    <row r="32" spans="2:27">
+      <c r="H32" s="58">
         <v>12</v>
       </c>
-      <c r="I32" s="64">
+      <c r="I32" s="59">
         <v>3</v>
       </c>
-      <c r="J32" s="64">
+      <c r="J32" s="59">
         <v>5</v>
       </c>
-      <c r="K32" s="65">
+      <c r="K32" s="60">
         <v>0</v>
       </c>
-      <c r="L32" s="65">
+      <c r="L32" s="60">
         <v>0</v>
       </c>
-      <c r="M32" s="65">
+      <c r="M32" s="60">
         <v>6.6752291587284098</v>
       </c>
-      <c r="N32" s="65">
+      <c r="N32" s="60">
         <v>0</v>
       </c>
-      <c r="O32" s="65">
+      <c r="O32" s="60">
         <v>-2.6021090804388902</v>
       </c>
-      <c r="P32" s="65">
+      <c r="P32" s="60">
         <v>1.8482986031311299</v>
       </c>
       <c r="Q32" s="48"/>
@@ -20346,35 +20372,35 @@
         <v>0.97065488032604175</v>
       </c>
     </row>
-    <row r="33" spans="6:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:23">
       <c r="F33" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="55">
         <v>1</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="56">
         <v>1</v>
       </c>
-      <c r="J33" s="61">
+      <c r="J33" s="56">
         <v>1</v>
       </c>
-      <c r="K33" s="62">
+      <c r="K33" s="57">
         <v>-3.10250451165843</v>
       </c>
-      <c r="L33" s="62">
+      <c r="L33" s="57">
         <v>0</v>
       </c>
-      <c r="M33" s="62">
+      <c r="M33" s="57">
         <v>0</v>
       </c>
-      <c r="N33" s="62">
+      <c r="N33" s="57">
         <v>0</v>
       </c>
-      <c r="O33" s="62">
+      <c r="O33" s="57">
         <v>3.99724211549856</v>
       </c>
-      <c r="P33" s="62">
+      <c r="P33" s="57">
         <v>0</v>
       </c>
       <c r="Q33" s="48"/>
@@ -20382,96 +20408,96 @@
         <v>0.29326126853667783</v>
       </c>
     </row>
-    <row r="34" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H34" s="60">
+    <row r="34" spans="6:23">
+      <c r="H34" s="55">
         <v>2</v>
       </c>
-      <c r="I34" s="61">
+      <c r="I34" s="56">
         <v>1</v>
       </c>
-      <c r="J34" s="61">
+      <c r="J34" s="56">
         <v>1</v>
       </c>
-      <c r="K34" s="62">
+      <c r="K34" s="57">
         <v>9.9042735781241102</v>
       </c>
-      <c r="L34" s="62">
+      <c r="L34" s="57">
         <v>0</v>
       </c>
-      <c r="M34" s="62">
+      <c r="M34" s="57">
         <v>-3.2783204774351402</v>
       </c>
-      <c r="N34" s="62">
+      <c r="N34" s="57">
         <v>0</v>
       </c>
-      <c r="O34" s="62">
+      <c r="O34" s="57">
         <v>0</v>
       </c>
-      <c r="P34" s="62">
+      <c r="P34" s="57">
         <v>0</v>
       </c>
       <c r="S34" s="53">
         <v>0.5757657808273613</v>
       </c>
     </row>
-    <row r="35" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H35" s="60">
+    <row r="35" spans="6:23">
+      <c r="H35" s="55">
         <v>3</v>
       </c>
-      <c r="I35" s="61">
+      <c r="I35" s="56">
         <v>1</v>
       </c>
-      <c r="J35" s="61">
+      <c r="J35" s="56">
         <v>1</v>
       </c>
-      <c r="K35" s="62">
+      <c r="K35" s="57">
         <v>0</v>
       </c>
-      <c r="L35" s="62">
+      <c r="L35" s="57">
         <v>0</v>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="57">
         <v>3.68017793076476</v>
       </c>
-      <c r="N35" s="62">
+      <c r="N35" s="57">
         <v>0</v>
       </c>
-      <c r="O35" s="62">
+      <c r="O35" s="57">
         <v>-1.93503777030206</v>
       </c>
-      <c r="P35" s="62">
+      <c r="P35" s="57">
         <v>0</v>
       </c>
       <c r="S35" s="53">
         <v>0.29763769265723561</v>
       </c>
     </row>
-    <row r="36" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H36" s="60">
+    <row r="36" spans="6:23">
+      <c r="H36" s="55">
         <v>4</v>
       </c>
-      <c r="I36" s="61">
+      <c r="I36" s="56">
         <v>2</v>
       </c>
-      <c r="J36" s="61">
+      <c r="J36" s="56">
         <v>2</v>
       </c>
-      <c r="K36" s="62">
+      <c r="K36" s="57">
         <v>0</v>
       </c>
-      <c r="L36" s="62">
+      <c r="L36" s="57">
         <v>0</v>
       </c>
-      <c r="M36" s="62">
+      <c r="M36" s="57">
         <v>1.17148199566441</v>
       </c>
-      <c r="N36" s="62">
+      <c r="N36" s="57">
         <v>-3.1093265920374198</v>
       </c>
-      <c r="O36" s="62">
+      <c r="O36" s="57">
         <v>0</v>
       </c>
-      <c r="P36" s="62">
+      <c r="P36" s="57">
         <v>5.4732323429833603</v>
       </c>
       <c r="R36" s="1"/>
@@ -20483,256 +20509,256 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H37" s="60">
+    <row r="37" spans="6:23">
+      <c r="H37" s="55">
         <v>5</v>
       </c>
-      <c r="I37" s="61">
+      <c r="I37" s="56">
         <v>3</v>
       </c>
-      <c r="J37" s="61">
+      <c r="J37" s="56">
         <v>3</v>
       </c>
-      <c r="K37" s="62">
+      <c r="K37" s="57">
         <v>4.8085392593805798</v>
       </c>
-      <c r="L37" s="62">
+      <c r="L37" s="57">
         <v>-2.3220186816543502</v>
       </c>
-      <c r="M37" s="62">
+      <c r="M37" s="57">
         <v>0</v>
       </c>
-      <c r="N37" s="62">
+      <c r="N37" s="57">
         <v>6.5993826321450699</v>
       </c>
-      <c r="O37" s="62">
+      <c r="O37" s="57">
         <v>0</v>
       </c>
-      <c r="P37" s="62">
+      <c r="P37" s="57">
         <v>0</v>
       </c>
       <c r="S37" s="53">
         <v>1.2639538987439054</v>
       </c>
     </row>
-    <row r="38" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H38" s="60">
+    <row r="38" spans="6:23">
+      <c r="H38" s="55">
         <v>6</v>
       </c>
-      <c r="I38" s="61">
+      <c r="I38" s="56">
         <v>3</v>
       </c>
-      <c r="J38" s="61">
+      <c r="J38" s="56">
         <v>4</v>
       </c>
-      <c r="K38" s="62">
+      <c r="K38" s="57">
         <v>0</v>
       </c>
-      <c r="L38" s="62">
+      <c r="L38" s="57">
         <v>5.2197399853786397</v>
       </c>
-      <c r="M38" s="62">
+      <c r="M38" s="57">
         <v>0</v>
       </c>
-      <c r="N38" s="62">
+      <c r="N38" s="57">
         <v>0</v>
       </c>
-      <c r="O38" s="62">
+      <c r="O38" s="57">
         <v>1.0817945982081201</v>
       </c>
-      <c r="P38" s="62">
+      <c r="P38" s="57">
         <v>-4.2103101763053097</v>
       </c>
       <c r="S38" s="53">
         <v>0.63286421392513237</v>
       </c>
     </row>
-    <row r="39" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H39" s="60">
+    <row r="39" spans="6:23">
+      <c r="H39" s="55">
         <v>7</v>
       </c>
-      <c r="I39" s="61">
+      <c r="I39" s="56">
         <v>1</v>
       </c>
-      <c r="J39" s="61">
+      <c r="J39" s="56">
         <v>1</v>
       </c>
-      <c r="K39" s="62">
+      <c r="K39" s="57">
         <v>0</v>
       </c>
-      <c r="L39" s="62">
+      <c r="L39" s="57">
         <v>-1.80924034829098</v>
       </c>
-      <c r="M39" s="62">
+      <c r="M39" s="57">
         <v>0</v>
       </c>
-      <c r="N39" s="62">
+      <c r="N39" s="57">
         <v>3.7820988705844898</v>
       </c>
-      <c r="O39" s="62">
+      <c r="O39" s="57">
         <v>0</v>
       </c>
-      <c r="P39" s="62">
+      <c r="P39" s="57">
         <v>0</v>
       </c>
       <c r="S39" s="53">
         <v>0.31168873326107177</v>
       </c>
     </row>
-    <row r="40" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H40" s="60">
+    <row r="40" spans="6:23">
+      <c r="H40" s="55">
         <v>8</v>
       </c>
-      <c r="I40" s="61">
+      <c r="I40" s="56">
         <v>1</v>
       </c>
-      <c r="J40" s="61">
+      <c r="J40" s="56">
         <v>1</v>
       </c>
-      <c r="K40" s="62">
+      <c r="K40" s="57">
         <v>17.490109282111298</v>
       </c>
-      <c r="L40" s="62">
+      <c r="L40" s="57">
         <v>0</v>
       </c>
-      <c r="M40" s="62">
+      <c r="M40" s="57">
         <v>-3.6801728672684701</v>
       </c>
-      <c r="N40" s="62">
+      <c r="N40" s="57">
         <v>0</v>
       </c>
-      <c r="O40" s="62">
+      <c r="O40" s="57">
         <v>0</v>
       </c>
-      <c r="P40" s="62">
+      <c r="P40" s="57">
         <v>0</v>
       </c>
       <c r="S40" s="53">
         <v>1.3658827098369288</v>
       </c>
     </row>
-    <row r="41" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H41" s="60">
+    <row r="41" spans="6:23">
+      <c r="H41" s="55">
         <v>9</v>
       </c>
-      <c r="I41" s="61">
+      <c r="I41" s="56">
         <v>1</v>
       </c>
-      <c r="J41" s="61">
+      <c r="J41" s="56">
         <v>1</v>
       </c>
-      <c r="K41" s="62">
+      <c r="K41" s="57">
         <v>0</v>
       </c>
-      <c r="L41" s="62">
+      <c r="L41" s="57">
         <v>3.1662117592799799</v>
       </c>
-      <c r="M41" s="62">
+      <c r="M41" s="57">
         <v>0</v>
       </c>
-      <c r="N41" s="62">
+      <c r="N41" s="57">
         <v>0</v>
       </c>
-      <c r="O41" s="62">
+      <c r="O41" s="57">
         <v>0</v>
       </c>
-      <c r="P41" s="62">
+      <c r="P41" s="57">
         <v>-2.5822444575364001</v>
       </c>
       <c r="S41" s="53">
         <v>0.27386384758273857</v>
       </c>
     </row>
-    <row r="42" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H42" s="60">
+    <row r="42" spans="6:23">
+      <c r="H42" s="55">
         <v>10</v>
       </c>
-      <c r="I42" s="61">
+      <c r="I42" s="56">
         <v>2</v>
       </c>
-      <c r="J42" s="61">
+      <c r="J42" s="56">
         <v>2</v>
       </c>
-      <c r="K42" s="62">
+      <c r="K42" s="57">
         <v>0</v>
       </c>
-      <c r="L42" s="62">
+      <c r="L42" s="57">
         <v>0</v>
       </c>
-      <c r="M42" s="62">
+      <c r="M42" s="57">
         <v>0.78389343190134497</v>
       </c>
-      <c r="N42" s="62">
+      <c r="N42" s="57">
         <v>-2.9131136569859502</v>
       </c>
-      <c r="O42" s="62">
+      <c r="O42" s="57">
         <v>0</v>
       </c>
-      <c r="P42" s="62">
+      <c r="P42" s="57">
         <v>4.9027648260490198</v>
       </c>
       <c r="S42" s="53">
         <v>0.34914351579706304</v>
       </c>
     </row>
-    <row r="43" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H43" s="60">
+    <row r="43" spans="6:23">
+      <c r="H43" s="55">
         <v>11</v>
       </c>
-      <c r="I43" s="61">
+      <c r="I43" s="56">
         <v>3</v>
       </c>
-      <c r="J43" s="61">
+      <c r="J43" s="56">
         <v>4</v>
       </c>
-      <c r="K43" s="62">
+      <c r="K43" s="57">
         <v>-5.1062334759296597</v>
       </c>
-      <c r="L43" s="62">
+      <c r="L43" s="57">
         <v>0.93277301965898096</v>
       </c>
-      <c r="M43" s="62">
+      <c r="M43" s="57">
         <v>0</v>
       </c>
-      <c r="N43" s="62">
+      <c r="N43" s="57">
         <v>0</v>
       </c>
-      <c r="O43" s="62">
+      <c r="O43" s="57">
         <v>6.4789032831356099</v>
       </c>
-      <c r="P43" s="62">
+      <c r="P43" s="57">
         <v>0</v>
       </c>
       <c r="S43" s="53">
         <v>0.66440382397957964</v>
       </c>
     </row>
-    <row r="44" spans="6:23" x14ac:dyDescent="0.2">
-      <c r="H44" s="60">
+    <row r="44" spans="6:23">
+      <c r="H44" s="55">
         <v>12</v>
       </c>
-      <c r="I44" s="61">
+      <c r="I44" s="56">
         <v>3</v>
       </c>
-      <c r="J44" s="61">
+      <c r="J44" s="56">
         <v>5</v>
       </c>
-      <c r="K44" s="62">
+      <c r="K44" s="57">
         <v>0</v>
       </c>
-      <c r="L44" s="62">
+      <c r="L44" s="57">
         <v>0</v>
       </c>
-      <c r="M44" s="62">
+      <c r="M44" s="57">
         <v>7.3189876971633296</v>
       </c>
-      <c r="N44" s="62">
+      <c r="N44" s="57">
         <v>0</v>
       </c>
-      <c r="O44" s="62">
+      <c r="O44" s="57">
         <v>-2.6975753228351702</v>
       </c>
-      <c r="P44" s="62">
+      <c r="P44" s="57">
         <v>1.74265800249307</v>
       </c>
       <c r="S44" s="53">
@@ -20741,11 +20767,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="K20:P20"/>
     <mergeCell ref="AB1:AC1"/>
@@ -20754,6 +20775,11 @@
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="T19:U19"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -20766,7 +20792,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B1:AC85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="1.1640625" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" customWidth="1"/>
@@ -20784,13 +20810,13 @@
     <col min="28" max="28" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB1" s="57" t="s">
+    <row r="1" spans="2:29">
+      <c r="AB1" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="57"/>
+      <c r="AC1" s="63"/>
     </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:29">
       <c r="AB2" s="45" t="s">
         <v>30</v>
       </c>
@@ -20798,15 +20824,15 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="S3" s="55" t="s">
+    <row r="3" spans="2:29">
+      <c r="S3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55" t="s">
+      <c r="T3" s="65"/>
+      <c r="U3" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="65"/>
       <c r="AB3" s="45" t="s">
         <v>31</v>
       </c>
@@ -20814,7 +20840,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:29">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -20826,38 +20852,38 @@
         <v>24</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58" t="s">
+      <c r="H4" s="61"/>
+      <c r="I4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58" t="s">
+      <c r="J4" s="61"/>
+      <c r="K4" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58" t="s">
+      <c r="L4" s="61"/>
+      <c r="M4" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="58"/>
-      <c r="O4" s="54" t="s">
+      <c r="N4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54" t="s">
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54" t="s">
+      <c r="R4" s="62"/>
+      <c r="S4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="62"/>
+      <c r="U4" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="54"/>
+      <c r="V4" s="62"/>
       <c r="W4" s="3"/>
       <c r="X4" s="2" t="s">
         <v>25</v>
@@ -20865,7 +20891,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:29">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -20945,7 +20971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:29">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -21031,7 +21057,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:29">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -21117,7 +21143,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:29">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -21203,7 +21229,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:29">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -21289,7 +21315,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:29">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -21375,7 +21401,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:29">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -21461,7 +21487,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:29">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -21541,7 +21567,7 @@
         <v>2.7733147409998602</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:29">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -21621,7 +21647,7 @@
         <v>1.98644662417039</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:29">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -21701,7 +21727,7 @@
         <v>-0.171158780969107</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:29">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -21781,7 +21807,7 @@
         <v>5.3875475690367098</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:29">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -21861,7 +21887,7 @@
         <v>2.4162494488161599</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -21941,31 +21967,31 @@
         <v>2.7314117620923599</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:27">
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="T19" s="55" t="s">
+    <row r="19" spans="2:27">
+      <c r="T19" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="U19" s="55"/>
+      <c r="U19" s="65"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27">
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="56" t="s">
+      <c r="K20" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
       <c r="Q20" s="10" t="s">
         <v>2</v>
       </c>
@@ -21974,7 +22000,7 @@
       </c>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:27">
       <c r="B21" s="9">
         <v>3</v>
       </c>
@@ -22025,7 +22051,7 @@
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:27">
       <c r="B22" s="9">
         <v>1</v>
       </c>
@@ -22072,7 +22098,7 @@
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:27">
       <c r="B23" s="9">
         <v>2</v>
       </c>
@@ -22123,7 +22149,7 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:27">
       <c r="B24" s="9">
         <v>1</v>
       </c>
@@ -22170,7 +22196,7 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:27">
       <c r="B25" s="9">
         <v>4</v>
       </c>
@@ -22220,7 +22246,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:27">
       <c r="B26" s="9">
         <v>1</v>
       </c>
@@ -22265,7 +22291,7 @@
         <v>0.26752979153965234</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:27">
       <c r="B27" s="9">
         <v>4</v>
       </c>
@@ -22310,7 +22336,7 @@
         <v>2.1096351101946853</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:27">
       <c r="B28" s="9">
         <v>1</v>
       </c>
@@ -22344,8 +22370,14 @@
       <c r="S28" s="19">
         <v>0.19999611559527547</v>
       </c>
+      <c r="T28" t="s">
+        <v>51</v>
+      </c>
+      <c r="U28">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:27">
       <c r="B29" s="9">
         <v>2</v>
       </c>
@@ -22380,8 +22412,14 @@
       <c r="S29" s="19">
         <v>0.19999935367617222</v>
       </c>
+      <c r="T29" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29">
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:27">
       <c r="B30" s="9">
         <v>1</v>
       </c>
@@ -22415,8 +22453,14 @@
       <c r="S30" s="19">
         <v>0.35595243505195723</v>
       </c>
+      <c r="T30" t="s">
+        <v>53</v>
+      </c>
+      <c r="U30">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:27">
       <c r="B31" s="9">
         <v>5</v>
       </c>
@@ -22454,7 +22498,7 @@
         <v>0.97063673355864366</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:27">
       <c r="B32" s="9">
         <v>1</v>
       </c>
@@ -22489,7 +22533,7 @@
         <v>0.19999505470329726</v>
       </c>
     </row>
-    <row r="36" spans="18:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="18:23">
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -22497,7 +22541,7 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="66" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:27">
       <c r="C66">
         <v>5</v>
       </c>
@@ -22574,7 +22618,7 @@
         <v>2.2190851642035998</v>
       </c>
     </row>
-    <row r="67" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:27">
       <c r="C67">
         <v>1</v>
       </c>
@@ -22651,7 +22695,7 @@
         <v>2.4830888945332799</v>
       </c>
     </row>
-    <row r="68" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:27">
       <c r="C68">
         <v>3</v>
       </c>
@@ -22728,7 +22772,7 @@
         <v>4.5172814906121896</v>
       </c>
     </row>
-    <row r="69" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:27">
       <c r="C69">
         <v>4</v>
       </c>
@@ -22805,7 +22849,7 @@
         <v>-0.55887107726871099</v>
       </c>
     </row>
-    <row r="70" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:27">
       <c r="C70">
         <v>6</v>
       </c>
@@ -22882,7 +22926,7 @@
         <v>1.93795380016014</v>
       </c>
     </row>
-    <row r="71" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:27">
       <c r="C71">
         <v>2</v>
       </c>
@@ -22959,7 +23003,7 @@
         <v>3.03659409158317</v>
       </c>
     </row>
-    <row r="73" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:27">
       <c r="C73">
         <f>C12</f>
         <v>5</v>
@@ -23061,7 +23105,7 @@
         <v>2.7733147409998602</v>
       </c>
     </row>
-    <row r="74" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:27">
       <c r="C74">
         <f t="shared" ref="C74:AA74" si="1">C13</f>
         <v>1</v>
@@ -23163,7 +23207,7 @@
         <v>1.98644662417039</v>
       </c>
     </row>
-    <row r="75" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:27">
       <c r="C75">
         <f t="shared" ref="C75:AA75" si="2">C14</f>
         <v>3</v>
@@ -23265,7 +23309,7 @@
         <v>-0.171158780969107</v>
       </c>
     </row>
-    <row r="76" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:27">
       <c r="C76">
         <f t="shared" ref="C76:AA76" si="3">C15</f>
         <v>4</v>
@@ -23367,7 +23411,7 @@
         <v>5.3875475690367098</v>
       </c>
     </row>
-    <row r="77" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:27">
       <c r="C77">
         <f t="shared" ref="C77:AA77" si="4">C16</f>
         <v>6</v>
@@ -23469,7 +23513,7 @@
         <v>2.4162494488161599</v>
       </c>
     </row>
-    <row r="78" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:27">
       <c r="C78">
         <f t="shared" ref="C78:AA78" si="5">C17</f>
         <v>2</v>
@@ -23571,7 +23615,7 @@
         <v>2.7314117620923599</v>
       </c>
     </row>
-    <row r="80" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:27">
       <c r="K80">
         <f t="shared" ref="K80:W80" si="6">K66-K73</f>
         <v>3.9559520834952897</v>
@@ -23641,7 +23685,7 @@
         <v>-0.55422957679626039</v>
       </c>
     </row>
-    <row r="81" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="11:27">
       <c r="K81">
         <f t="shared" ref="K81:W81" si="8">K67-K74</f>
         <v>0.52816506115212025</v>
@@ -23711,7 +23755,7 @@
         <v>0.49664227036288988</v>
       </c>
     </row>
-    <row r="82" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="11:27">
       <c r="K82">
         <f t="shared" ref="K82:W82" si="10">K68-K75</f>
         <v>3.7486052230173526</v>
@@ -23781,7 +23825,7 @@
         <v>4.6884402715812969</v>
       </c>
     </row>
-    <row r="83" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="83" spans="11:27">
       <c r="K83">
         <f t="shared" ref="K83:W83" si="12">K69-K76</f>
         <v>-3.3171904466463049</v>
@@ -23851,7 +23895,7 @@
         <v>-5.9464186463054212</v>
       </c>
     </row>
-    <row r="84" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="11:27">
       <c r="K84">
         <f t="shared" ref="K84:W84" si="14">K70-K77</f>
         <v>-0.65439188094494982</v>
@@ -23921,7 +23965,7 @@
         <v>-0.47829564865601992</v>
       </c>
     </row>
-    <row r="85" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="85" spans="11:27">
       <c r="K85">
         <f t="shared" ref="K85:W85" si="16">K71-K78</f>
         <v>-4.2608925419828427</v>
@@ -23993,11 +24037,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
@@ -24006,6 +24045,11 @@
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="T19:U19"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -24018,7 +24062,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B1:AC85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="1.1640625" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" customWidth="1"/>
@@ -24036,13 +24080,13 @@
     <col min="28" max="28" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB1" s="57" t="s">
+    <row r="1" spans="2:29">
+      <c r="AB1" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="57"/>
+      <c r="AC1" s="63"/>
     </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:29">
       <c r="AB2" s="45" t="s">
         <v>30</v>
       </c>
@@ -24050,15 +24094,15 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="S3" s="55" t="s">
+    <row r="3" spans="2:29">
+      <c r="S3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55" t="s">
+      <c r="T3" s="65"/>
+      <c r="U3" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="65"/>
       <c r="AB3" s="45" t="s">
         <v>31</v>
       </c>
@@ -24066,7 +24110,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:29">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -24078,38 +24122,38 @@
         <v>24</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58" t="s">
+      <c r="H4" s="61"/>
+      <c r="I4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58" t="s">
+      <c r="J4" s="61"/>
+      <c r="K4" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58" t="s">
+      <c r="L4" s="61"/>
+      <c r="M4" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="58"/>
-      <c r="O4" s="54" t="s">
+      <c r="N4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54" t="s">
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54" t="s">
+      <c r="R4" s="62"/>
+      <c r="S4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="62"/>
+      <c r="U4" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="54"/>
+      <c r="V4" s="62"/>
       <c r="W4" s="3"/>
       <c r="X4" s="2" t="s">
         <v>25</v>
@@ -24117,7 +24161,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:29">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -24197,7 +24241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:29">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -24283,7 +24327,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:29">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -24369,7 +24413,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:29">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -24455,7 +24499,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:29">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -24541,7 +24585,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:29">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -24627,7 +24671,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:29">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -24713,7 +24757,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:29">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -24793,7 +24837,7 @@
         <v>2.56232850029759</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:29">
       <c r="B13" t="s">
         <v>18</v>
       </c>
@@ -24873,7 +24917,7 @@
         <v>1.2739585226486401</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:29">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -24953,7 +24997,7 @@
         <v>-1.8538109652486701</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:29">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -25033,7 +25077,7 @@
         <v>8.9943471772222008</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:29">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -25113,7 +25157,7 @@
         <v>2.3957909648440201</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -25193,31 +25237,31 @@
         <v>3.5323840605753398</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:27">
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="T19" s="55" t="s">
+    <row r="19" spans="2:27">
+      <c r="T19" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="U19" s="55"/>
+      <c r="U19" s="65"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27">
       <c r="G20" t="s">
         <v>38</v>
       </c>
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="56" t="s">
+      <c r="K20" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
       <c r="Q20" s="10" t="s">
         <v>2</v>
       </c>
@@ -25226,7 +25270,7 @@
       </c>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:27">
       <c r="F21" s="49"/>
       <c r="G21" s="9">
         <v>1</v>
@@ -25272,7 +25316,7 @@
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:27">
       <c r="F22" s="49"/>
       <c r="G22" s="9">
         <v>1</v>
@@ -25317,7 +25361,7 @@
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:27">
       <c r="F23" s="49"/>
       <c r="G23" s="9">
         <v>1</v>
@@ -25365,7 +25409,7 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:27">
       <c r="F24" s="49"/>
       <c r="G24" s="9">
         <v>2</v>
@@ -25410,7 +25454,7 @@
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:27">
       <c r="F25" s="49"/>
       <c r="G25" s="9">
         <v>3</v>
@@ -25455,7 +25499,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:27">
       <c r="F26" s="49"/>
       <c r="G26" s="9">
         <v>4</v>
@@ -25498,7 +25542,7 @@
         <v>0.24700877925089718</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:27">
       <c r="F27" s="49"/>
       <c r="G27" s="9">
         <v>1</v>
@@ -25538,7 +25582,7 @@
         <v>1.8872380703049458</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:27">
       <c r="F28" s="49"/>
       <c r="G28" s="9">
         <v>1</v>
@@ -25570,8 +25614,14 @@
       <c r="S28" s="19">
         <v>0.34139571791083523</v>
       </c>
+      <c r="T28" t="s">
+        <v>51</v>
+      </c>
+      <c r="U28">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:27">
       <c r="F29" s="49"/>
       <c r="G29" s="9">
         <v>1</v>
@@ -25603,8 +25653,14 @@
       <c r="S29" s="19">
         <v>0.2</v>
       </c>
+      <c r="T29" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29">
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:27">
       <c r="F30" s="49"/>
       <c r="G30" s="9">
         <v>2</v>
@@ -25636,8 +25692,14 @@
       <c r="S30" s="19">
         <v>0.47691220387075506</v>
       </c>
+      <c r="T30" t="s">
+        <v>53</v>
+      </c>
+      <c r="U30">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:27">
       <c r="F31" s="49"/>
       <c r="G31" s="9">
         <v>4</v>
@@ -25670,7 +25732,7 @@
         <v>0.45140664060326563</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:27">
       <c r="G32" s="9">
         <v>5</v>
       </c>
@@ -25703,7 +25765,7 @@
         <v>0.71891144618569292</v>
       </c>
     </row>
-    <row r="36" spans="18:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="18:23">
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -25711,7 +25773,7 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="66" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:27">
       <c r="C66">
         <v>5</v>
       </c>
@@ -25788,7 +25850,7 @@
         <v>2.2190851642035998</v>
       </c>
     </row>
-    <row r="67" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:27">
       <c r="C67">
         <v>1</v>
       </c>
@@ -25865,7 +25927,7 @@
         <v>2.4830888945332799</v>
       </c>
     </row>
-    <row r="68" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:27">
       <c r="C68">
         <v>3</v>
       </c>
@@ -25942,7 +26004,7 @@
         <v>4.5172814906121896</v>
       </c>
     </row>
-    <row r="69" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:27">
       <c r="C69">
         <v>4</v>
       </c>
@@ -26019,7 +26081,7 @@
         <v>-0.55887107726871099</v>
       </c>
     </row>
-    <row r="70" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:27">
       <c r="C70">
         <v>6</v>
       </c>
@@ -26096,7 +26158,7 @@
         <v>1.93795380016014</v>
       </c>
     </row>
-    <row r="71" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:27">
       <c r="C71">
         <v>2</v>
       </c>
@@ -26173,7 +26235,7 @@
         <v>3.03659409158317</v>
       </c>
     </row>
-    <row r="73" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:27">
       <c r="C73">
         <f>C12</f>
         <v>5</v>
@@ -26275,7 +26337,7 @@
         <v>2.56232850029759</v>
       </c>
     </row>
-    <row r="74" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:27">
       <c r="C74">
         <f t="shared" ref="C74:AA78" si="1">C13</f>
         <v>1</v>
@@ -26377,7 +26439,7 @@
         <v>1.2739585226486401</v>
       </c>
     </row>
-    <row r="75" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:27">
       <c r="C75">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -26479,7 +26541,7 @@
         <v>-1.8538109652486701</v>
       </c>
     </row>
-    <row r="76" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:27">
       <c r="C76">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -26581,7 +26643,7 @@
         <v>8.9943471772222008</v>
       </c>
     </row>
-    <row r="77" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:27">
       <c r="C77">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -26683,7 +26745,7 @@
         <v>2.3957909648440201</v>
       </c>
     </row>
-    <row r="78" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:27">
       <c r="C78">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -26785,7 +26847,7 @@
         <v>3.5323840605753398</v>
       </c>
     </row>
-    <row r="80" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:27">
       <c r="K80">
         <f t="shared" ref="K80:W80" si="2">K66-K73</f>
         <v>4.388469395900338</v>
@@ -26855,7 +26917,7 @@
         <v>-0.34324333609399016</v>
       </c>
     </row>
-    <row r="81" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="11:27">
       <c r="K81">
         <f t="shared" ref="K81:W81" si="4">K67-K74</f>
         <v>1.48154273712281</v>
@@ -26925,7 +26987,7 @@
         <v>1.2091303718846398</v>
       </c>
     </row>
-    <row r="82" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="11:27">
       <c r="K82">
         <f t="shared" ref="K82:W82" si="5">K68-K75</f>
         <v>4.120711741221128</v>
@@ -26995,7 +27057,7 @@
         <v>6.3710924558608593</v>
       </c>
     </row>
-    <row r="83" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="83" spans="11:27">
       <c r="K83">
         <f t="shared" ref="K83:W83" si="6">K69-K76</f>
         <v>-1.5360692627744252</v>
@@ -27065,7 +27127,7 @@
         <v>-9.5532182544909112</v>
       </c>
     </row>
-    <row r="84" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="11:27">
       <c r="K84">
         <f t="shared" ref="K84:W84" si="7">K70-K77</f>
         <v>0.69813223011958003</v>
@@ -27135,7 +27197,7 @@
         <v>-0.45783716468388014</v>
       </c>
     </row>
-    <row r="85" spans="11:27" x14ac:dyDescent="0.2">
+    <row r="85" spans="11:27">
       <c r="K85">
         <f t="shared" ref="K85:W85" si="8">K71-K78</f>
         <v>-1.9297505422238532</v>
@@ -27207,11 +27269,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="K20:P20"/>
     <mergeCell ref="T19:U19"/>
@@ -27220,17 +27277,13 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:T4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329284A6-3054-BC42-9C55-98C2892A1A61}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>